--- a/data/merged/2026-09-23/MERGED_ES_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_ES_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -1281,13 +1281,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1305,50 +1305,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Product 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1690,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR8"/>
+  <dimension ref="A1:BR7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2830,56 +2786,52 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Tamaño: 16 L</t>
-        </is>
-      </c>
+          <t>B0H9LVZZV1</t>
+        </is>
+      </c>
+      <c r="D5" s="14"/>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Marca: Cecotec | Función especial: Húmedo/seco | Tipo de filtro: Sistema de filtración doble | Recomendación de superficie: Todos los suelos | Fuente de alimentación: Eléctrico con cable | Voltaje: 1200 Voltios | Componentes incluidos: 1 x Aspiradora; 1 x Accesorio para esquinas; 1 x Accesorio 2 en 1; 1 x Base de aspiración universal; 1 x Cargador; 1 x Cepillo para el suelo; 1 x Manual de instrucciones; 1 x Tubo extensible; 1 x Tubo flexible | ¿Es inalámbrico?: No | Peso del producto: 4,5 Kilogramos | Capacidad: 16 litros</t>
+          <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Vataje: 250 vatios | Factor de forma: Palo | Color: Blanco | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plus. 1200W, Ligero, Compacto, Doble Función de Succión y Soplado, Accesorios</t>
+          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, Blanco</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de sólidos y líquidos de gran potencia con tanque de plástico para aspirar todo tipo de suciedad, incluidos líquidos, de cualquier rincón de tu hogar.
-Aspira sin esfuerzo gracias a su potencia de 1200 W y a su reducido peso y tamaño.
-Sistema de doble filtrado que filtra el agua y purifica el aire reteniendo de forma eficaz un gran porcentaje de alérgenos. Incluye función sopladora Blowing System.
-Gran radio de acción con más de 5 metros y porta accesorios para poder limpiar de la forma más cómoda hasta el último rincón.
-Incluye 4 accesorios para limpiar cualquier superficie de forma eficaz.</t>
+          <t>AHORRA TIEMPO CON LIMPIEZA 2 EN 1: aspira y friega de una pasada y en la mitad de tiempo, en comparación con el tradicional aspirado y fregado (basado en pruebas internas en comparación con el aspirado y fregado tradicionales)
+ACABA CON LA SUCIEDAD DIARIA: elimina el polvo, la suciedad y los líquidos en una sola pasada con una fuerte succión, una potente presión de fregado y el agua sucia recogida en un depósito separado
+MANTÉN LOS SUELOS LIMPIOS, UNIFORMES Y SIN MARCAS: el sistema automático escurre el agua sucia del rodillo mientras se suministra agua limpia continuamente, ayudando a conseguir resultados de calidad
+RELÁJATE GRACIAS A UN MANTENIMIENTO SIN ESFUERZO: ahorra tiempo después de cada tarea con la limpieza con agua caliente, la autolimpieza, el secado con aire caliente y el sistema antienredos de pelo
+CONTENIDO DE ENVÍO: Fregona aspiradora con mango ergonómico, filtro, cepillo de limpieza y batería potente</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D2KT41N3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H9LVZZV1?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0D33D9J3P</t>
+          <t>B0H9LVZZV1</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -2893,13 +2845,13 @@
         </is>
       </c>
       <c r="O5" s="15">
-        <v>1650</v>
+        <v>355242</v>
       </c>
       <c r="P5" s="15">
-        <v>-49</v>
+        <v>-34487</v>
       </c>
       <c r="Q5" s="16">
-        <v>-0.03</v>
+        <v>-6.13</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -2908,79 +2860,63 @@
       </c>
       <c r="S5" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T5" s="15">
-        <v>533</v>
-      </c>
-      <c r="U5" s="16">
-        <v>1.28</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="U5" s="16"/>
       <c r="V5" s="15">
-        <v>17578</v>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="X5" s="15">
-        <v>15960</v>
-      </c>
+        <v>3591</v>
+      </c>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
       <c r="Y5" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="20">
-        <v>32.98</v>
+        <v>399</v>
       </c>
       <c r="AA5" s="4"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="19">
-        <v>940</v>
+        <v>33</v>
       </c>
       <c r="AE5" s="15">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="AF5" s="21">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AG5" s="22">
-        <v>0.0901</v>
+        <v>0.22219999999999998</v>
       </c>
       <c r="AH5" s="20">
-        <v>10.1</v>
+        <v>12.61</v>
       </c>
       <c r="AI5" s="16">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="AJ5"/>
       <c r="AK5" s="13" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AL5" s="19">
-        <v>880</v>
+        <v>43</v>
       </c>
       <c r="AM5" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN5" s="13" t="inlineStr">
-        <is>
-          <t>17天</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
-      <c r="AP5" s="20">
-        <v>69.35</v>
-      </c>
-      <c r="AQ5" s="19">
-        <v>10</v>
-      </c>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="19"/>
       <c r="AR5" s="19">
         <v>1</v>
       </c>
@@ -2991,17 +2927,13 @@
       </c>
       <c r="AT5" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU5" s="13"/>
       <c r="AV5" s="14"/>
       <c r="AW5" s="13"/>
-      <c r="AX5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AX5" s="13"/>
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
@@ -3011,54 +2943,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD5" s="13"/>
       <c r="BE5" s="13"/>
-      <c r="BF5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
       <c r="BH5" s="14"/>
       <c r="BI5"/>
       <c r="BJ5" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilogramos</t>
+          <t>8,5 Kilogramos</t>
         </is>
       </c>
       <c r="BK5" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>8.50 kg</t>
         </is>
       </c>
       <c r="BL5" s="23" t="inlineStr">
         <is>
-          <t>38l. x 33an. x 45al. centímetros</t>
+          <t>35,9l. x 30,4an. x 115,8al. centímetros</t>
         </is>
       </c>
       <c r="BM5" s="23"/>
       <c r="BN5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>10.51 kg</t>
         </is>
       </c>
       <c r="BO5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>10.51 kg</t>
         </is>
       </c>
       <c r="BP5" s="23" t="inlineStr">
         <is>
-          <t>40 x 36 x 36 cm</t>
+          <t>79 x 34 x 32 cm</t>
         </is>
       </c>
       <c r="BQ5" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 36.00 x 36.00 cm</t>
+          <t>79.00 x 34.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BR5" s="13" t="inlineStr">
@@ -3074,52 +2998,56 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0H9LVZZV1</t>
-        </is>
-      </c>
-      <c r="D6" s="14"/>
+          <t>B0DGV9F4X3</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Nombre de estilo: X-CLEAN 4 Negro</t>
+        </is>
+      </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Vataje: 250 vatios | Factor de forma: Palo | Color: Blanco | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH</t>
+          <t>Marca: Rowenta | Función especial: Inalámbrico | Tipo de filtro: Filtro de espuma, Filtro HEPA | Recomendación de superficie: Parquet, Mármol, Laminado, Azulejos | Fuente de alimentación: Batería | Voltaje: 18,5 Voltios | Componentes incluidos: Rodillo suave, rodillo recurrente, filtro tipo HEPA adicional, filtro de espuma adicional, cepillo de limpieza con función colador y función cortador | ¿Es inalámbrico?: Sí | Peso del producto: 5,4 Kilogramos | Capacidad: 1,1 litros</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Rowenta</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, Blanco</t>
+          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, Negro</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>AHORRA TIEMPO CON LIMPIEZA 2 EN 1: aspira y friega de una pasada y en la mitad de tiempo, en comparación con el tradicional aspirado y fregado (basado en pruebas internas en comparación con el aspirado y fregado tradicionales)
-ACABA CON LA SUCIEDAD DIARIA: elimina el polvo, la suciedad y los líquidos en una sola pasada con una fuerte succión, una potente presión de fregado y el agua sucia recogida en un depósito separado
-MANTÉN LOS SUELOS LIMPIOS, UNIFORMES Y SIN MARCAS: el sistema automático escurre el agua sucia del rodillo mientras se suministra agua limpia continuamente, ayudando a conseguir resultados de calidad
-RELÁJATE GRACIAS A UN MANTENIMIENTO SIN ESFUERZO: ahorra tiempo después de cada tarea con la limpieza con agua caliente, la autolimpieza, el secado con aire caliente y el sistema antienredos de pelo
-CONTENIDO DE ENVÍO: Fregona aspiradora con mango ergonómico, filtro, cepillo de limpieza y batería potente</t>
+          <t>LIMPIEZA 2 EN 1: fregona eléctricainalámbrica para limpieza seca y húmeda que permite ganar tiempo aspirando y fregando enuna sola pasada, para unos resultados óptimos en todo tipo de suelos duros (madera, mármol, laminados y baldosas)
+DETECCIÓN INTELIGENTE DE LA SUCIEDAD: detección automática de la suciedad con indicadores de color en una pantalla led (rojo para la suciedad y azul cuando detecta un suelo limpio) y un ajuste automático de la velocidad de rotación del rodillo y del flujo de agua para conseguir unos óptimosresultados
+GRAN AUTONOMÍA: limpieza sin cables que marca la diferencia, con hasta 50min de autonomía para cubrir hasta 350m²dependiendo del mobiliario de la casa
+LIMPIEZA SIN ESFUERZO:diseño moderno, ligero, tan solo 1,1kg en tu mano, inteligente,con un sistema de rodillos ayudados por las ruedas, siendo necesario utilizar solo un 25 %del esfuerzo habitual
+SISTEMA DE AUTOLIMPIEZA:activa la función con tan solo pulsar un botón y, una vez lavado el rodillo, solo tienes que dejarlopreviamente secarpara que esté listo para la siguiente sesión de limpieza mientras se carga en la base</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H9LVZZV1?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0H9LVZZV1</t>
+          <t>B0DKMVFHRN</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -3133,13 +3061,13 @@
         </is>
       </c>
       <c r="O6" s="15">
-        <v>355242</v>
+        <v>232936</v>
       </c>
       <c r="P6" s="15">
-        <v>-34487</v>
+        <v>-12404</v>
       </c>
       <c r="Q6" s="16">
-        <v>-6.13</v>
+        <v>-0.06</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -3148,53 +3076,49 @@
       </c>
       <c r="S6" s="18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T6" s="15">
-        <v>9</v>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T6" s="15"/>
       <c r="U6" s="16"/>
-      <c r="V6" s="15">
-        <v>3591</v>
-      </c>
+      <c r="V6" s="15"/>
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
       <c r="Y6" s="19">
         <v>1</v>
       </c>
       <c r="Z6" s="20">
-        <v>399</v>
+        <v>173.74</v>
       </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="19">
-        <v>33</v>
+        <v>816</v>
       </c>
       <c r="AE6" s="15">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AF6" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG6" s="22">
-        <v>0.22219999999999998</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="20">
-        <v>12.61</v>
+        <v>11.58</v>
       </c>
       <c r="AI6" s="16">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AJ6"/>
       <c r="AK6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AL6" s="19">
-        <v>43</v>
+        <v>684</v>
       </c>
       <c r="AM6" s="13" t="inlineStr">
         <is>
@@ -3204,9 +3128,11 @@
       <c r="AN6" s="13"/>
       <c r="AO6" s="13"/>
       <c r="AP6" s="20"/>
-      <c r="AQ6" s="19"/>
+      <c r="AQ6" s="19">
+        <v>10</v>
+      </c>
       <c r="AR6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS6" s="14" t="inlineStr">
         <is>
@@ -3231,46 +3157,54 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD6" s="13"/>
+      <c r="BD6" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
+      <c r="BF6" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG6" s="13"/>
       <c r="BH6" s="14"/>
       <c r="BI6"/>
       <c r="BJ6" s="23" t="inlineStr">
         <is>
-          <t>8,5 Kilogramos</t>
+          <t>5,4 Kilogramos</t>
         </is>
       </c>
       <c r="BK6" s="23" t="inlineStr">
         <is>
-          <t>8.50 kg</t>
+          <t>5.40 kg</t>
         </is>
       </c>
       <c r="BL6" s="23" t="inlineStr">
         <is>
-          <t>35,9l. x 30,4an. x 115,8al. centímetros</t>
+          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
         </is>
       </c>
       <c r="BM6" s="23"/>
       <c r="BN6" s="23" t="inlineStr">
         <is>
-          <t>10.51 kg</t>
+          <t>7.52 kg</t>
         </is>
       </c>
       <c r="BO6" s="23" t="inlineStr">
         <is>
-          <t>10.51 kg</t>
+          <t>7.52 kg</t>
         </is>
       </c>
       <c r="BP6" s="23" t="inlineStr">
         <is>
-          <t>79 x 34 x 32 cm</t>
+          <t>75.8 x 33 x 28.8 cm</t>
         </is>
       </c>
       <c r="BQ6" s="23" t="inlineStr">
         <is>
-          <t>79.00 x 34.00 x 32.00 cm</t>
+          <t>75.80 x 33.00 x 28.80 cm</t>
         </is>
       </c>
       <c r="BR6" s="13" t="inlineStr">
@@ -3286,56 +3220,52 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0DGV9F4X3</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Nombre de estilo: X-CLEAN 4 Negro</t>
-        </is>
-      </c>
+          <t>B0H9LQCPJ9</t>
+        </is>
+      </c>
+      <c r="D7" s="14"/>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Marca: Rowenta | Función especial: Inalámbrico | Tipo de filtro: Filtro de espuma, Filtro HEPA | Recomendación de superficie: Parquet, Mármol, Laminado, Azulejos | Fuente de alimentación: Batería | Voltaje: 18,5 Voltios | Componentes incluidos: Rodillo suave, rodillo recurrente, filtro tipo HEPA adicional, filtro de espuma adicional, cepillo de limpieza con función colador y función cortador | ¿Es inalámbrico?: Sí | Peso del producto: 5,4 Kilogramos | Capacidad: 1,1 litros</t>
+          <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Color: Negro | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH | Número de productos: 1</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Rowenta</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, Negro</t>
+          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en Negro</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>LIMPIEZA 2 EN 1: fregona eléctricainalámbrica para limpieza seca y húmeda que permite ganar tiempo aspirando y fregando enuna sola pasada, para unos resultados óptimos en todo tipo de suelos duros (madera, mármol, laminados y baldosas)
-DETECCIÓN INTELIGENTE DE LA SUCIEDAD: detección automática de la suciedad con indicadores de color en una pantalla led (rojo para la suciedad y azul cuando detecta un suelo limpio) y un ajuste automático de la velocidad de rotación del rodillo y del flujo de agua para conseguir unos óptimosresultados
-GRAN AUTONOMÍA: limpieza sin cables que marca la diferencia, con hasta 50min de autonomía para cubrir hasta 350m²dependiendo del mobiliario de la casa
-LIMPIEZA SIN ESFUERZO:diseño moderno, ligero, tan solo 1,1kg en tu mano, inteligente,con un sistema de rodillos ayudados por las ruedas, siendo necesario utilizar solo un 25 %del esfuerzo habitual
-SISTEMA DE AUTOLIMPIEZA:activa la función con tan solo pulsar un botón y, una vez lavado el rodillo, solo tienes que dejarlopreviamente secarpara que esté listo para la siguiente sesión de limpieza mientras se carga en la base</t>
+          <t>AHORRA TIEMPO CON LIMPIEZA 2 EN 1: aspira y friega de una pasada y en la mitad de tiempo, en comparación con el tradicional aspirado y fregado (basado en pruebas internas en comparación con el aspirado y fregado tradicionales)
+ACABA CON LA SUCIEDAD DIARIA: elimina el polvo, la suciedad y los líquidos en una sola pasada con una fuerte succión, una potente presión de fregado y el agua sucia recogida en un depósito separado
+MANTÉN LOS SUELOS LIMPIOS, UNIFORMES Y SIN MARCAS: el sistema automático escurre el agua sucia del rodillo mientras se suministra agua limpia continuamente, ayudando a conseguir resultados de calidad
+RELÁJATE GRACIAS A UN MANTENIMIENTO SIN ESFUERZO: ahorra tiempo después de cada tarea con la limpieza con agua caliente, la autolimpieza, el secado con aire caliente y el sistema antienredos de pelo
+CONTENIDO DE ENVÍO: Fregona aspiradora con mango ergonómico, filtro, cepillo de limpieza y batería potente</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H9LQCPJ9?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0DKMVFHRN</t>
+          <t>B0H9LQCPJ9</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -3349,13 +3279,11 @@
         </is>
       </c>
       <c r="O7" s="15">
-        <v>232936</v>
-      </c>
-      <c r="P7" s="15">
-        <v>-12404</v>
-      </c>
+        <v>360793</v>
+      </c>
+      <c r="P7" s="15"/>
       <c r="Q7" s="16">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -3364,7 +3292,7 @@
       </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T7" s="15"/>
@@ -3375,39 +3303,27 @@
       <c r="Y7" s="19">
         <v>1</v>
       </c>
-      <c r="Z7" s="20">
-        <v>173.74</v>
-      </c>
+      <c r="Z7" s="20"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="19">
-        <v>816</v>
-      </c>
-      <c r="AE7" s="15">
-        <v>35</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="AE7" s="15"/>
       <c r="AF7" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG7" s="22">
         <v>0</v>
       </c>
-      <c r="AH7" s="20">
-        <v>11.58</v>
-      </c>
+      <c r="AH7" s="20"/>
       <c r="AI7" s="16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AJ7"/>
-      <c r="AK7" s="13" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AL7" s="19">
-        <v>684</v>
-      </c>
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="19"/>
       <c r="AM7" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -3416,17 +3332,9 @@
       <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
       <c r="AP7" s="20"/>
-      <c r="AQ7" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR7" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS7" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="AQ7" s="19"/>
+      <c r="AR7" s="19"/>
+      <c r="AS7" s="14"/>
       <c r="AT7" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -3445,229 +3353,33 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD7" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD7" s="13"/>
       <c r="BE7" s="13"/>
-      <c r="BF7" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
       <c r="BH7" s="14"/>
       <c r="BI7"/>
       <c r="BJ7" s="23" t="inlineStr">
         <is>
-          <t>5,4 Kilogramos</t>
+          <t>8,5 Kilogramos</t>
         </is>
       </c>
       <c r="BK7" s="23" t="inlineStr">
         <is>
-          <t>5.40 kg</t>
+          <t>8.50 kg</t>
         </is>
       </c>
       <c r="BL7" s="23" t="inlineStr">
         <is>
-          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
+          <t>35,9l. x 30,4an. x 115,8al. centímetros</t>
         </is>
       </c>
       <c r="BM7" s="23"/>
-      <c r="BN7" s="23" t="inlineStr">
-        <is>
-          <t>7.52 kg</t>
-        </is>
-      </c>
-      <c r="BO7" s="23" t="inlineStr">
-        <is>
-          <t>7.52 kg</t>
-        </is>
-      </c>
-      <c r="BP7" s="23" t="inlineStr">
-        <is>
-          <t>75.8 x 33 x 28.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ7" s="23" t="inlineStr">
-        <is>
-          <t>75.80 x 33.00 x 28.80 cm</t>
-        </is>
-      </c>
-      <c r="BR7" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>B0H9LQCPJ9</t>
-        </is>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Color: Negro | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH | Número de productos: 1</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en Negro</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>AHORRA TIEMPO CON LIMPIEZA 2 EN 1: aspira y friega de una pasada y en la mitad de tiempo, en comparación con el tradicional aspirado y fregado (basado en pruebas internas en comparación con el aspirado y fregado tradicionales)
-ACABA CON LA SUCIEDAD DIARIA: elimina el polvo, la suciedad y los líquidos en una sola pasada con una fuerte succión, una potente presión de fregado y el agua sucia recogida en un depósito separado
-MANTÉN LOS SUELOS LIMPIOS, UNIFORMES Y SIN MARCAS: el sistema automático escurre el agua sucia del rodillo mientras se suministra agua limpia continuamente, ayudando a conseguir resultados de calidad
-RELÁJATE GRACIAS A UN MANTENIMIENTO SIN ESFUERZO: ahorra tiempo después de cada tarea con la limpieza con agua caliente, la autolimpieza, el secado con aire caliente y el sistema antienredos de pelo
-CONTENIDO DE ENVÍO: Fregona aspiradora con mango ergonómico, filtro, cepillo de limpieza y batería potente</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0H9LQCPJ9?psc=1</t>
-        </is>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>B0H9LQCPJ9</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O8" s="15">
-        <v>360793</v>
-      </c>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16">
-        <v>0</v>
-      </c>
-      <c r="R8" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T8" s="15"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="19">
-        <v>30</v>
-      </c>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="20"/>
-      <c r="AI8" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ8"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN8" s="13"/>
-      <c r="AO8" s="13"/>
-      <c r="AP8" s="20"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="14"/>
-      <c r="AT8" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="14"/>
-      <c r="AW8" s="13"/>
-      <c r="AX8" s="13"/>
-      <c r="AY8" s="13"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="13"/>
-      <c r="BC8" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD8" s="13"/>
-      <c r="BE8" s="13"/>
-      <c r="BF8" s="13"/>
-      <c r="BG8" s="13"/>
-      <c r="BH8" s="14"/>
-      <c r="BI8"/>
-      <c r="BJ8" s="23" t="inlineStr">
-        <is>
-          <t>8,5 Kilogramos</t>
-        </is>
-      </c>
-      <c r="BK8" s="23" t="inlineStr">
-        <is>
-          <t>8.50 kg</t>
-        </is>
-      </c>
-      <c r="BL8" s="23" t="inlineStr">
-        <is>
-          <t>35,9l. x 30,4an. x 115,8al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM8" s="23"/>
-      <c r="BN8" s="23"/>
-      <c r="BO8" s="23"/>
-      <c r="BP8" s="23"/>
-      <c r="BQ8" s="23"/>
-      <c r="BR8" s="13"/>
+      <c r="BN7" s="23"/>
+      <c r="BO7" s="23"/>
+      <c r="BP7" s="23"/>
+      <c r="BQ7" s="23"/>
+      <c r="BR7" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3694,42 +3406,35 @@
     <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.es/dp/B0H633WR96"/>
     <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N4" r:id="rId21"/>
-    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0D2KT41N3?psc=1"/>
-    <hyperlink ref="K5" r:id="rId25" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg"/>
-    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0D33D9J3P"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
     <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N5" r:id="rId28"/>
-    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
-    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
-    <hyperlink ref="K6" r:id="rId32" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg"/>
-    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
+    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K6" r:id="rId32" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0DKMVFHRN"/>
     <hyperlink ref="M6" r:id="rId34" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N6" r:id="rId35"/>
-    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K7" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg"/>
-    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0DKMVFHRN"/>
+    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
+    <hyperlink ref="K7" r:id="rId39" tooltip="https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
     <hyperlink ref="M7" r:id="rId41" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N7" r:id="rId42"/>
-    <hyperlink ref="C8" r:id="rId43" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
-    <hyperlink ref="G8" r:id="rId44" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J8" r:id="rId45" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
-    <hyperlink ref="K8" r:id="rId46" tooltip="https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId47" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
-    <hyperlink ref="M8" r:id="rId48" tooltip="https://www.amazon.es/b?node=218878925031"/>
-    <hyperlink ref="N8" r:id="rId49"/>
   </hyperlinks>
-  <drawing r:id="rId50"/>
+  <drawing r:id="rId43"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -3793,7 +3498,7 @@
         <v>280.1703910614525</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5056497175141242</v>
+        <v>0.8108720271800679</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3814,49 +3519,28 @@
         <v>385.75949367088606</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1115819209039548</v>
+        <v>0.17893544733861835</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B4" s="15">
-        <v>533</v>
+        <v>9</v>
       </c>
       <c r="C4" s="15">
-        <v>17578</v>
+        <v>3591</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>32.97936210131332</v>
+        <v>399.0</v>
       </c>
       <c r="G4" s="22">
-        <v>0.3764124293785311</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <v>9</v>
-      </c>
-      <c r="C5" s="15">
-        <v>3591</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20">
-        <v>399.0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.006355932203389831</v>
+        <v>0.010192525481313703</v>
       </c>
     </row>
   </sheetData>
@@ -3920,15 +3604,15 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>1416</v>
+        <v>883</v>
       </c>
       <c r="C2" s="15">
-        <v>282721</v>
+        <v>265143</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>199.6617231638418</v>
+        <v>300.27519818799544</v>
       </c>
       <c r="G2" s="22">
         <v>1.0</v>
